--- a/Project/DiceWarrior/LubanTool/Datas/global.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17470"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <t>##</t>
   </si>
   <si>
-    <t>#x6</t>
+    <t>#1</t>
   </si>
   <si>
     <t>(map#sep=|,),int#ref=TbItemCategory,int</t>
@@ -51,7 +51,7 @@
     <t>100001|10,100002|10</t>
   </si>
   <si>
-    <t>#x7</t>
+    <t>#2</t>
   </si>
   <si>
     <t>(list#sep=|),int</t>
@@ -1066,7 +1066,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="40.75" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
@@ -1228,7 +1228,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Project/DiceWarrior/LubanTool/Datas/global.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/global.xlsx
@@ -100,10 +100,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -259,7 +267,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,8 +276,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor theme="4" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
       </patternFill>
     </fill>
     <fill>
@@ -459,11 +479,163 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="21">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -585,76 +757,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -663,10 +829,10 @@
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -675,10 +841,10 @@
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -687,10 +853,10 @@
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -699,10 +865,10 @@
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -711,19 +877,88 @@
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -731,10 +966,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1066,153 +1298,222 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="40.75" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="37.375" customWidth="1"/>
-    <col min="4" max="4" width="49.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.625"/>
+    <col min="1" max="1" width="16.5833333333333" customWidth="1"/>
+    <col min="2" max="2" width="39.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="24.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" customHeight="1" spans="1:4">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:4">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+    <row r="3" customHeight="1" spans="1:4">
+      <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
+    <row r="4" customHeight="1" spans="1:4">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:4">
+      <c r="A5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:4">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="D5" s="17"/>
+    </row>
+    <row r="6" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:4">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:4">
-      <c r="A9" s="1" t="s">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:4">
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:4">
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:4">
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:4">
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:4">
-      <c r="D14" s="5"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:4">
-      <c r="B25" s="3"/>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:4">
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:4">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:4">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:4">
+      <c r="A22" s="18"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:4">
+      <c r="A23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="1:4">
+      <c r="B25" s="24"/>
       <c r="C25"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="6"/>
-    </row>
-    <row r="31" ht="21" customHeight="1"/>
-    <row r="32" spans="1:4">
-      <c r="D32" s="3"/>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="39" customFormat="1" spans="2:4">
-      <c r="B39" s="3"/>
+      <c r="D25" s="24"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:4">
+      <c r="A26" s="26"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:4">
+      <c r="D32" s="24"/>
+    </row>
+    <row r="33" customHeight="1" spans="2:4">
+      <c r="B33" s="24"/>
+      <c r="D33" s="24"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="2:4">
+      <c r="B39" s="24"/>
       <c r="C39"/>
-      <c r="D39" s="3"/>
+      <c r="D39" s="24"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D32">
